--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.67126160854096</v>
+        <v>8.721580011387907</v>
       </c>
       <c r="D2" t="n">
-        <v>43.9551769846459</v>
+        <v>7.142716260004958</v>
       </c>
       <c r="E2" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F2" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.85545453505087</v>
+        <v>7.126511361945767</v>
       </c>
       <c r="D3" t="n">
-        <v>35.20227797309391</v>
+        <v>5.720370170627761</v>
       </c>
       <c r="E3" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F3" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.73628789649313</v>
+        <v>6.294646783180134</v>
       </c>
       <c r="D4" t="n">
-        <v>26.3362479713037</v>
+        <v>4.279640295336852</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F4" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.19609330034845</v>
+        <v>3.119365161306623</v>
       </c>
       <c r="D5" t="n">
-        <v>31.71080075317576</v>
+        <v>5.153005122391062</v>
       </c>
       <c r="E5" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F5" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.75394704043941</v>
+        <v>3.860016394071404</v>
       </c>
       <c r="D6" t="n">
-        <v>19.27764361580766</v>
+        <v>3.132617087568745</v>
       </c>
       <c r="E6" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F6" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.44059037540382</v>
+        <v>3.646595936003121</v>
       </c>
       <c r="D7" t="n">
-        <v>46.22761754075331</v>
+        <v>7.511987850372413</v>
       </c>
       <c r="E7" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F7" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.3486242525108</v>
+        <v>4.281651441033004</v>
       </c>
       <c r="D8" t="n">
-        <v>53.20856354542849</v>
+        <v>8.64639157613213</v>
       </c>
       <c r="E8" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F8" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>7.941806156074898</v>
+        <v>1.290543500362171</v>
       </c>
       <c r="D9" t="n">
-        <v>32.51525560219456</v>
+        <v>5.283729035356617</v>
       </c>
       <c r="E9" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F9" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.00270845985259</v>
+        <v>4.062940124726046</v>
       </c>
       <c r="D10" t="n">
-        <v>35.00357124637428</v>
+        <v>5.68808032753582</v>
       </c>
       <c r="E10" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F10" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.91892431568863</v>
+        <v>2.749325201299403</v>
       </c>
       <c r="D11" t="n">
-        <v>26.10956820702803</v>
+        <v>4.242804833642055</v>
       </c>
       <c r="E11" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F11" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.74754878398196</v>
+        <v>2.071476677397069</v>
       </c>
       <c r="D12" t="n">
-        <v>33.49451723320072</v>
+        <v>5.442859050395118</v>
       </c>
       <c r="E12" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F12" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.38279023649707</v>
+        <v>2.499703413430774</v>
       </c>
       <c r="D13" t="n">
-        <v>7.514155404991906</v>
+        <v>1.221050253311185</v>
       </c>
       <c r="E13" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F13" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>14.36618176958698</v>
+        <v>2.334504537557885</v>
       </c>
       <c r="D14" t="n">
-        <v>15.73826121099494</v>
+        <v>2.557467446786678</v>
       </c>
       <c r="E14" t="n">
-        <v>12.77071458400574</v>
+        <v>2.075241119900933</v>
       </c>
       <c r="F14" t="n">
-        <v>12.09704495079604</v>
+        <v>1.965769804504356</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
